--- a/survey_templates/046_personal_finance_survey--survey_templates.xlsx
+++ b/survey_templates/046_personal_finance_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>personal_income_1</t>
+          <t>annual_income</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,35 +543,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>family_size_1</t>
+          <t>employment_status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>family_size</t>
+          <t>Employment status</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>annual_savings_1</t>
+          <t>income_source</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annual savings</t>
+          <t>Income source</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>employment_status_1</t>
+          <t>annual_savings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Employment status</t>
+          <t>Annual savings</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>annual_savings_2</t>
+          <t>family_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annual savings</t>
+          <t>Is this information about an individual or a family?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>income_source_1</t>
+          <t>annual_expense_budget</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Income source</t>
+          <t>Annual expense budget</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>annual_savings_3</t>
+          <t>outstanding_debt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annual savings</t>
+          <t>Do you have any outstanding debt?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>family_member_1</t>
+          <t>annual_savings_percentage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Is this information about an individual or a family?</t>
+          <t>Annual savings as a percentage of income</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>income_source_2</t>
+          <t>employment_type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Income source</t>
+          <t>Employment type</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>annual_savings_4</t>
+          <t>dependents</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Annual savings</t>
+          <t>Do you have any dependents?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,16 +750,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>annual_savings_5</t>
+          <t>annual_savings_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Annual savings</t>
+          <t>Annual Savings 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>income_source_2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Income Source 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -804,306 +827,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>family_size_1_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>family_size_1_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>family_size_1_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>family_size_1_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employment_status_1_choices</t>
+          <t>income_source_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>wages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>Wages</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employment_status_1_choices</t>
+          <t>income_source_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>self-employed</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Self-employed</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>employment_status_1_choices</t>
+          <t>income_source_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>student</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>employment_status_1_choices</t>
+          <t>income_source_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>employment_status_1_choices</t>
+          <t>family_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>income_source_1_choices</t>
+          <t>family_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wages</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wages</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>income_source_1_choices</t>
+          <t>outstanding_debt_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>income_source_1_choices</t>
+          <t>outstanding_debt_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>income_source_1_choices</t>
+          <t>employment_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>family_member_1_choices</t>
+          <t>employment_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>individual</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>family_member_1_choices</t>
+          <t>employment_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Contractor</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_source_2_choices</t>
+          <t>employment_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wages</t>
+          <t>freelancer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wages</t>
+          <t>Freelancer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_source_2_choices</t>
+          <t>dependents_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>investments</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Investments</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_source_2_choices</t>
+          <t>dependents_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1115,10 +1138,61 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>wages</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>income_source_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>income_source_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>income_source_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
